--- a/imageCreationExcel/Bright/Master/MASTER_0.xlsx
+++ b/imageCreationExcel/Bright/Master/MASTER_0.xlsx
@@ -606,15 +606,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\8_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>M_0_2_S_filler_8_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_0_2_S_filler_8_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -660,15 +666,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\0_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>M_0_3_2_unmatch_0_day_rain_busy_MODEL.jpg</t>
+          <t>M_0_3_2_unmatch_0_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -714,15 +738,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\7_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>M_0_4_B_filler_7_day_sun_busy_MODEL.jpg</t>
+          <t>M_0_4_B_filler_7_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -822,15 +864,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\8_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>M_0_6_R_filler_8_day_rain_empty_MODEL.jpg</t>
+          <t>M_0_6_R_filler_8_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -876,15 +936,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\6_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>M_0_7_6_match_6_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_0_7_6_match_6_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -930,15 +996,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\7_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>M_0_8_C_filler_7_day_rain_empty_MODEL.jpg</t>
+          <t>M_0_8_C_filler_7_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -984,15 +1068,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\5_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>M_0_9_S_filler_5_day_sun_busy_MODEL.jpg</t>
+          <t>M_0_9_S_filler_5_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -1038,15 +1140,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\4_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>M_0_10_B_filler_4_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_0_10_B_filler_4_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -1092,15 +1200,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\3_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>M_0_11_3_match_3_day_sun_empty_MODEL.jpg</t>
+          <t>M_0_11_3_match_3_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -1254,15 +1380,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\8_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>M_0_14_B_filler_8_day_rain_empty_MODEL.jpg</t>
+          <t>M_0_14_B_filler_8_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -1362,15 +1506,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\6_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>M_0_16_L_filler_6_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_0_16_L_filler_6_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -1416,15 +1566,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\7_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>M_0_17_7_match_7_day_sun_busy_MODEL.jpg</t>
+          <t>M_0_17_7_match_7_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -1524,15 +1692,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\3_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>M_0_19_3_match_3_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_0_19_3_match_3_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -1632,15 +1806,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\0_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>M_0_21_S_filler_0_day_sun_busy_MODEL.jpg</t>
+          <t>M_0_21_S_filler_0_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -1740,15 +1932,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\5_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>M_0_23_L_filler_5_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_0_23_L_filler_5_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -1794,15 +1992,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\4_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>M_0_24_4_match_4_day_sun_empty_MODEL.jpg</t>
+          <t>M_0_24_4_match_4_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -1848,15 +2064,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\5_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>M_0_25_U_filler_5_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_0_25_U_filler_5_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -1902,15 +2124,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\1_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>M_0_26_3_unmatch_1_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_0_26_3_unmatch_1_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -1956,15 +2184,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\2_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>M_0_27_A_filler_2_day_rain_busy_MODEL.jpg</t>
+          <t>M_0_27_A_filler_2_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -2010,15 +2256,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\9_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>M_0_28_F_filler_9_day_sun_busy_MODEL.jpg</t>
+          <t>M_0_28_F_filler_9_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -2118,15 +2382,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\8_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>M_0_30_C_filler_8_day_rain_empty_MODEL.jpg</t>
+          <t>M_0_30_C_filler_8_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -2172,15 +2454,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\4_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>M_0_31_J_filler_4_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_0_31_J_filler_4_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -2226,15 +2514,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\4_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>M_0_32_6_unmatch_4_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_0_32_6_unmatch_4_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -2388,15 +2682,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\9_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>M_0_35_T_filler_9_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_0_35_T_filler_9_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -2496,15 +2796,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\8_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>M_0_37_D_filler_8_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_0_37_D_filler_8_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -2550,15 +2856,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\5_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>M_0_38_I_filler_5_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_0_38_I_filler_5_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -2658,15 +2970,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\6_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>M_0_40_A_filler_6_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_0_40_A_filler_6_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -2712,15 +3030,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\7_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>M_0_41_7_match_7_day_rain_empty_MODEL.jpg</t>
+          <t>M_0_41_7_match_7_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -2874,15 +3210,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\5_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>M_0_44_1_unmatch_5_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_0_44_1_unmatch_5_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -2928,15 +3270,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\3_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>M_0_45_J_filler_3_day_rain_busy_MODEL.jpg</t>
+          <t>M_0_45_J_filler_3_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -3036,15 +3396,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\1_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>M_0_47_C_filler_1_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_0_47_C_filler_1_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -3090,15 +3456,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\4_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>M_0_48_4_match_4_day_rain_empty_MODEL.jpg</t>
+          <t>M_0_48_4_match_4_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
